--- a/data/trans_orig/IP31A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31A-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32012</t>
+          <t>32199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40730</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55671</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23163</t>
+          <t>22924</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>38843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25767</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40887</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55074</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89140</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109859</t>
+          <t>110681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15869</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46017</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74169</t>
+          <t>73105</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35846</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35696</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>25263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39099</t>
+          <t>38933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34431</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52398</t>
+          <t>51824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70930</t>
+          <t>70943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29975</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46706</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14141</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32514</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46400</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26854</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>37951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>64987</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22605</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>37542</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>29314</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43987</t>
+          <t>43174</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>53619</t>
+          <t>54899</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>71882</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44958</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>62005</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>102846</t>
+          <t>103959</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>128012</t>
+          <t>127785</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>24205</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40325</t>
+          <t>39534</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>55314</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>77378</t>
+          <t>77269</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>37369</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>52184</t>
+          <t>53216</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>74016</t>
+          <t>75838</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>51088</t>
+          <t>51661</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>69957</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>51711</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>69365</t>
+          <t>70069</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>109044</t>
+          <t>106976</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>133815</t>
+          <t>133271</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>54073</t>
+          <t>54217</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>76921</t>
+          <t>78029</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24144</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>77144</t>
+          <t>76393</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>104259</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>129962</t>
+          <t>128794</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>163040</t>
+          <t>162635</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>216187</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>258192</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>277624</t>
+          <t>277982</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>317411</t>
+          <t>316381</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>290545</t>
+          <t>289380</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>330352</t>
+          <t>330766</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>580239</t>
+          <t>581618</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>636357</t>
+          <t>636317</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>145592</t>
+          <t>145990</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>179385</t>
+          <t>180674</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>121191</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>154309</t>
+          <t>156329</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>275191</t>
+          <t>277810</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>323239</t>
+          <t>324054</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>32258</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>51239</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30003</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28948</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44578</t>
+          <t>44794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59045</t>
+          <t>59635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60484</t>
+          <t>60665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93397</t>
+          <t>94915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114872</t>
+          <t>115402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25544</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25080</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>23593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33997</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42636</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>53752</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>73070</t>
+          <t>72799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44968</t>
+          <t>45521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>36499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>55965</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>30294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44768</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51916</t>
+          <t>52205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71320</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38306</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22574</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>42882</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34007</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30117</t>
+          <t>29871</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>32567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43850</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59255</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14592</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>28314</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>48185</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>67062</t>
+          <t>66794</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>61715</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>116944</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>142808</t>
+          <t>141719</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>43606</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>26532</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>42862</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>57443</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>80402</t>
+          <t>81475</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>30446</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>48258</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>47901</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>70158</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>68644</t>
+          <t>68451</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86504</t>
+          <t>86934</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>82047</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>136475</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>164311</t>
+          <t>164399</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>46560</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>67850</t>
+          <t>69854</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>102636</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>114402</t>
+          <t>115127</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>149786</t>
+          <t>150184</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>200103</t>
+          <t>198261</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>244383</t>
+          <t>242770</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>274558</t>
+          <t>274571</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>315817</t>
+          <t>314002</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>315919</t>
+          <t>316588</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>358500</t>
+          <t>357465</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>604219</t>
+          <t>604640</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>660975</t>
+          <t>658406</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>147506</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>182488</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>127184</t>
+          <t>124118</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>158929</t>
+          <t>159274</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>284380</t>
+          <t>282586</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>331643</t>
+          <t>332522</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29985</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>48819</t>
+          <t>50114</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>51071</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>76195</t>
+          <t>77721</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54720</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>42265</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50475</t>
+          <t>49805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48895</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74374</t>
+          <t>74166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95162</t>
+          <t>94408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45952</t>
+          <t>46956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66143</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31922</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>58495</t>
+          <t>58997</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>24510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>24411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>44332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24942</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17235</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>38143</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29345</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31813</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>55757</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>28713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64640</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31407</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59763</t>
+          <t>58922</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,37%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30670</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>789</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51514</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>66651</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>57997</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>73859</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>113546</t>
+          <t>114019</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>136363</t>
+          <t>137587</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>40087</t>
+          <t>40543</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33558</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>48302</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>70052</t>
+          <t>68984</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>19378</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11957</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23904</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>41911</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>76861</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>95430</t>
+          <t>94472</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>84302</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>102751</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>165987</t>
+          <t>166080</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>191625</t>
+          <t>193013</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>26041</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>41280</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>40512</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>54939</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>77648</t>
+          <t>77169</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49649</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>73021</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>69355</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>98856</t>
+          <t>99014</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>126880</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>163794</t>
+          <t>164429</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>290351</t>
+          <t>290461</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>331169</t>
+          <t>328551</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>312317</t>
+          <t>312503</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>353543</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>615312</t>
+          <t>615551</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>670914</t>
+          <t>672474</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>142594</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>175718</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>147728</t>
+          <t>147562</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>184975</t>
+          <t>183915</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>298482</t>
+          <t>297469</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>349991</t>
+          <t>348133</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80365</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>111073</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
